--- a/artfynd/A 62453-2023 artfynd.xlsx
+++ b/artfynd/A 62453-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448404</v>
+        <v>120448401</v>
       </c>
       <c r="B2" t="n">
         <v>57336</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478102</v>
+        <v>478256</v>
       </c>
       <c r="R2" t="n">
-        <v>7069936</v>
+        <v>7069879</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448401</v>
+        <v>120448386</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478256</v>
+        <v>477930</v>
       </c>
       <c r="R3" t="n">
-        <v>7069879</v>
+        <v>7070058</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448386</v>
+        <v>120448404</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477930</v>
+        <v>478102</v>
       </c>
       <c r="R4" t="n">
-        <v>7070058</v>
+        <v>7069936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62453-2023 artfynd.xlsx
+++ b/artfynd/A 62453-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448401</v>
+        <v>120448404</v>
       </c>
       <c r="B2" t="n">
         <v>57336</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478256</v>
+        <v>478102</v>
       </c>
       <c r="R2" t="n">
-        <v>7069879</v>
+        <v>7069936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448386</v>
+        <v>120448401</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477930</v>
+        <v>478256</v>
       </c>
       <c r="R3" t="n">
-        <v>7070058</v>
+        <v>7069879</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448404</v>
+        <v>120448386</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478102</v>
+        <v>477930</v>
       </c>
       <c r="R4" t="n">
-        <v>7069936</v>
+        <v>7070058</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62453-2023 artfynd.xlsx
+++ b/artfynd/A 62453-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448401</v>
+        <v>120448386</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478256</v>
+        <v>477930</v>
       </c>
       <c r="R3" t="n">
-        <v>7069879</v>
+        <v>7070058</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448386</v>
+        <v>120448401</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477930</v>
+        <v>478256</v>
       </c>
       <c r="R4" t="n">
-        <v>7070058</v>
+        <v>7069879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62453-2023 artfynd.xlsx
+++ b/artfynd/A 62453-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448404</v>
+        <v>120448386</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478102</v>
+        <v>477930</v>
       </c>
       <c r="R2" t="n">
-        <v>7069936</v>
+        <v>7070058</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448386</v>
+        <v>120448401</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477930</v>
+        <v>478256</v>
       </c>
       <c r="R3" t="n">
-        <v>7070058</v>
+        <v>7069879</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448401</v>
+        <v>120448404</v>
       </c>
       <c r="B4" t="n">
         <v>57336</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478256</v>
+        <v>478102</v>
       </c>
       <c r="R4" t="n">
-        <v>7069879</v>
+        <v>7069936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62453-2023 artfynd.xlsx
+++ b/artfynd/A 62453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120448386</v>
+        <v>120257834</v>
       </c>
       <c r="B2" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477930</v>
+        <v>477600</v>
       </c>
       <c r="R2" t="n">
-        <v>7070058</v>
+        <v>7070170</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120448404</v>
+        <v>120257835</v>
       </c>
       <c r="B3" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478102</v>
+        <v>477527</v>
       </c>
       <c r="R3" t="n">
-        <v>7069936</v>
+        <v>7070165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448401</v>
+        <v>120448411</v>
       </c>
       <c r="B4" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478256</v>
+        <v>477983</v>
       </c>
       <c r="R4" t="n">
-        <v>7069879</v>
+        <v>7070006</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +942,6 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -993,6 +963,1409 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120448362</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478040</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7070022</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120448363</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477624</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7070201</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120448412</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477985</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7070008</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120448422</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477835</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7070170</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120448423</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477940</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7070194</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120448401</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478256</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7069879</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120448404</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478102</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7069936</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120257828</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>477694</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7070217</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120448365</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477749</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7070184</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120448366</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>477735</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7070184</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120448385</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477947</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7070192</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120448386</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477930</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7070058</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120448389</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478063</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7069971</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120448397</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jontebodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478158</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7069813</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62453-2023 artfynd.xlsx
+++ b/artfynd/A 62453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120257834</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120257835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448362</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448363</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448412</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448422</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448423</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448404</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120257828</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448365</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448366</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448385</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448386</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448389</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,8 +2451,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448397</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>